--- a/StructureDefinition-Urval-analysmetod-laboratoriemedicin.xlsx
+++ b/StructureDefinition-Urval-analysmetod-laboratoriemedicin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Urval-analysmetod-laboratoriemedicin.xlsx
+++ b/StructureDefinition-Urval-analysmetod-laboratoriemedicin.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Supporting logical model generated from gloo4.xmi (source class: Urval analysmetod laboratoriemedicin).</t>
+    <t>Urval ur Snomed CT (OID: 1.2.752.116.2.1.1) för att beskriva metodprinciper inom laboratoriemedicin. Princip för analysmetod bör användas för laboratoriemedicinska undersökningar där resultaten kan skilja sig beroende på analysmetoden, även om man avser att mäta samma sak, eller när metodprincipen är viktig för tolkningen av resultatet.
+OID: 1.2.752.129.5.1.18
+Refset-ID: 63181000052104</t>
   </si>
   <si>
     <t>Purpose</t>
